--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderMainTemplate.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseOrderMainTemplate.xlsx
@@ -225,7 +225,19 @@
     <t>是否加急</t>
   </si>
   <si>
-    <t>新品首批</t>
+    <r>
+      <t>*</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>新品首批</t>
+    </r>
   </si>
   <si>
     <t>备注</t>
@@ -1246,7 +1258,7 @@
       <c r="O1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
       <c r="Q1" t="s">
@@ -1255,11 +1267,11 @@
     </row>
   </sheetData>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:N$1048576 O$1:O$1048576">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P2:P1048576">
+      <formula1>"试产首批,量产首批,试量产首批,非首批"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N$1:O$1048576">
       <formula1>"是,否"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P$1:P$1048576">
-      <formula1>"试产首批,量产首批,试量产首批,非首批"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
